--- a/excel/import_nganh.xlsx
+++ b/excel/import_nganh.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HK2_NAM_3\Mo_Hinh_Phan_Lop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HK2_NAM_3\Mo_Hinh_Phan_Lop\DO_AN\QuanLyTuyenSinh\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910B3E97-8999-42CB-8D26-78D1C3F9228A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F21C1FD-CFF3-436D-BECB-F29BBAA571E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{09D70DB4-558C-4ECA-8E4F-57B2AB017FC7}"/>
   </bookViews>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
-  <si>
-    <t>DANH SÁCH NGÀNH</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>STT</t>
   </si>
@@ -141,11 +138,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{584C84F8-8AF7-4AF5-8D4E-C4C7C2409E35}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="25.5546875" customWidth="1"/>
@@ -470,98 +464,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B2">
+        <v>800034</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>10</v>
+      </c>
+      <c r="O2">
         <v>12</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>800001</v>
+        <v>800035</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>199</v>
+      </c>
+      <c r="F3">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
@@ -570,57 +592,57 @@
         <v>18</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M3">
+        <v>30</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3">
-        <v>10</v>
-      </c>
       <c r="O3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>800002</v>
+        <v>800036</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
       </c>
       <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -629,57 +651,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>800003</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>188</v>
-      </c>
-      <c r="F5">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>67</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>